--- a/forms/trg/Formulir_TRG_agribac.xlsx
+++ b/forms/trg/Formulir_TRG_agribac.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B52)</f>
+        <f>COUNTA(Anggota!B5:B53)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F52)</f>
+        <f>COUNTA(Anggota!F5:F53)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Tutik Kuswinanti, M.Sc.</t>
+          <t>Prof. Dr. Sc. Agr. Ir. Baharuddin</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Mycology</t>
+          <t>Biotechnology; Bacteriology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,17 +937,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-1202-3853</t>
+          <t>0000-0002-5109-8090</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6015408</t>
+          <t>6016070</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>55792741300</t>
+          <t>57202610804</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,37 +962,41 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Muh. Jayadi, M.P.</t>
+          <t>Prof. Dr. Ir. Tutik Kuswinanti, M.Sc.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Department of Soil Science, Faculty of Agriculture, Hasanuddin University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Soil Fertility</t>
+          <t>Mycology</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>0009-0005-1202-3853</t>
+        </is>
+      </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6013090</t>
+          <t>6015408</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57126469300</t>
+          <t>55792741300</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1007,23 +1011,39 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Fachirah Ulfa, M.P.</t>
+          <t>Prof. Dr. Ir. Muh. Jayadi, M.P.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="11" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Department of Soil Science, Faculty of Agriculture, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Soil Fertility</t>
+        </is>
+      </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6013090</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>57126469300</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1036,12 +1056,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Junaid, S.P., M.P., Ph.D.</t>
+          <t>Prof. Dr. Ir. Fachirah Ulfa, M.P.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1065,12 +1085,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Asman, S.P., M.P., Ph.D.</t>
+          <t>Muhammad Junaid, S.P., M.P., Ph.D.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1094,24 +1114,16 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Nur Mujahidin, S.P., M.Si.</t>
+          <t>Asman, S.P., M.P., Ph.D.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>Bacteriology</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -1131,12 +1143,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Zaraswati Dwyana Zainuddin, M.Si.</t>
+          <t>Nur Mujahidin, S.P., M.Si.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1146,24 +1158,16 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Microbiology</t>
+          <t>Bacteriology</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-5002-237X</t>
-        </is>
-      </c>
+      <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>58793481800</t>
-        </is>
-      </c>
+      <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1176,12 +1180,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Juhriah, M.Si.</t>
+          <t>Dr. Zaraswati Dwyana Zainuddin, M.Si.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1189,14 +1193,26 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E12" s="11" t="n"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Microbiology</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-5002-237X</t>
+        </is>
+      </c>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>58793481800</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1209,12 +1225,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. A. Masniawati, M.Si.</t>
+          <t>Dr. Juhriah, M.Si.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1222,11 +1238,7 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
-      </c>
+      <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
@@ -1246,12 +1258,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dr. Nurfadila JS, S.Pd.</t>
+          <t>Dr. A. Masniawati, M.Si.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1259,7 +1271,11 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E14" s="11" t="n"/>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -1279,12 +1295,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Andi Muliarni Okasa, S.P.,M.Si.</t>
+          <t>Dr. Nurfadila JS, S.Pd.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1292,11 +1308,7 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Plant Breeding and Biotechnology</t>
-        </is>
-      </c>
+      <c r="E15" s="11" t="n"/>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1316,22 +1328,22 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Prof. Riyazali Zafaralli Sayed</t>
+          <t>Andi Muliarni Okasa, S.P.,M.Si.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>University of Nizwa, Sultanate of Oman</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Microbiology</t>
+          <t>Plant Breeding and Biotechnology</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1353,22 +1365,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Prof. Madya Dr. Khairulmazmi Bin Ahmad</t>
+          <t>Prof. Riyazali Zafaralli Sayed</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Universiti Putra Malaysia</t>
+          <t>University of Nizwa, Sultanate of Oman</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Plant Pathology and Biological Sciences</t>
+          <t>Microbiology</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1390,39 +1402,31 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ann M. Stevens, M.S., Ph.D.</t>
+          <t>Prof. Madya Dr. Khairulmazmi Bin Ahmad</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Virginia Polytechnic Institute and State University, USA</t>
+          <t>Universiti Putra Malaysia</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Molecular Microbiology</t>
+          <t>Plant Pathology and Biological Sciences</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-4942-0124</t>
-        </is>
-      </c>
+      <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>55568518936</t>
-        </is>
-      </c>
+      <c r="L18" s="12" t="n"/>
       <c r="M18" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1435,31 +1439,39 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Dr. Zulfitriany Dwiyanti Mustaka, S.P., M.P.</t>
+          <t>Prof. Ann M. Stevens, M.S., Ph.D.</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Politeknik Pertanian Negeri Pangkajene dan Kepulauan</t>
+          <t>Virginia Polytechnic Institute and State University, USA</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Agroindustry</t>
+          <t>Molecular Microbiology</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-4942-0124</t>
+        </is>
+      </c>
       <c r="K19" s="12" t="n"/>
-      <c r="L19" s="12" t="n"/>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>55568518936</t>
+        </is>
+      </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1472,22 +1484,22 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Dr. rer. nat. Sarjiya Antonius</t>
+          <t>Dr. Zulfitriany Dwiyanti Mustaka, S.P., M.P.</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovational Agency (BRIN)</t>
+          <t>Politeknik Pertanian Negeri Pangkajene dan Kepulauan</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Applied Microbiology</t>
+          <t>Agroindustry</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1509,29 +1521,29 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Dr. Suriani</t>
+          <t>Dr. rer. nat. Sarjiya Antonius</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>National Research and Innovational Agency (BRIN)</t>
+        </is>
+      </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovation Agency</t>
+          <t>Applied Microbiology</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n"/>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-8781-221X</t>
-        </is>
-      </c>
+      <c r="J21" s="12" t="n"/>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="11" t="inlineStr">
@@ -1546,29 +1558,29 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Sri Sudewi</t>
+          <t>Dr. Suriani</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>National Research and Innovation Agency</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>Microbiology</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="12" t="n"/>
       <c r="H22" s="12" t="n"/>
       <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-8781-221X</t>
+        </is>
+      </c>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="11" t="inlineStr">
@@ -1583,22 +1595,22 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Fadyah Khamila Sahlan</t>
+          <t>Sri Sudewi</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>National Research and Innovation Agency</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Bacteriology</t>
+          <t>Microbiology</t>
         </is>
       </c>
       <c r="F23" s="12" t="n"/>
@@ -1620,16 +1632,24 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Ade Sugiarti Kumalasari</t>
+          <t>Fadyah Khamila Sahlan</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="11" t="n"/>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Bacteriology</t>
+        </is>
+      </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
@@ -1649,20 +1669,16 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Elisurya Ibrahim</t>
+          <t>Ade Sugiarti Kumalasari</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>National Research and Innovational Agency (BRIN)</t>
-        </is>
-      </c>
+      <c r="E25" s="11" t="n"/>
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="12" t="n"/>
       <c r="H25" s="12" t="n"/>
@@ -1682,20 +1698,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Gaby Maulida Nurdin</t>
+          <t>Elisurya Ibrahim</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="n"/>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>National Research and Innovational Agency (BRIN)</t>
+        </is>
+      </c>
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="12" t="n"/>
       <c r="H26" s="12" t="n"/>
@@ -1715,12 +1731,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Akhmad Syakur</t>
+          <t>Gaby Maulida Nurdin</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -1748,12 +1764,12 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Rispan Ady</t>
+          <t>Akhmad Syakur</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -1781,12 +1797,12 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Salensia Haryati Afonso</t>
+          <t>Muhammad Rispan Ady</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -1814,12 +1830,12 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Junaidi</t>
+          <t>Salensia Haryati Afonso</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -1847,12 +1863,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Pratiwi Hamzah</t>
+          <t>Junaidi</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -1880,12 +1896,12 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Suharman</t>
+          <t>Pratiwi Hamzah</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -1913,12 +1929,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Rezki Meylansari Rosli</t>
+          <t>Suharman</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -1946,12 +1962,12 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Andi Dinda Namirah Sarilla</t>
+          <t>Rezki Meylansari Rosli</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -1979,12 +1995,12 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Aminah</t>
+          <t>Andi Dinda Namirah Sarilla</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -2012,12 +2028,12 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Dian Meylani</t>
+          <t>Aminah</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -2025,11 +2041,7 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>Bacteriology</t>
-        </is>
-      </c>
+      <c r="E36" s="11" t="n"/>
       <c r="F36" s="12" t="n"/>
       <c r="G36" s="12" t="n"/>
       <c r="H36" s="12" t="n"/>
@@ -2049,12 +2061,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Tenriati</t>
+          <t>Dian Meylani</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -2086,12 +2098,12 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Gracia Monteiro de Almeida</t>
+          <t>Tenriati</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -2123,12 +2135,12 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Otilio Soares Monteiro</t>
+          <t>Gracia Monteiro de Almeida</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -2160,22 +2172,22 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Fita Dewi Yuniar</t>
+          <t>Otilio Soares Monteiro</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
           <t>Bacteriology</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>AgriBac Team</t>
         </is>
       </c>
       <c r="F40" s="12" t="n"/>
@@ -2183,11 +2195,7 @@
       <c r="H40" s="12" t="n"/>
       <c r="I40" s="12" t="n"/>
       <c r="J40" s="12" t="n"/>
-      <c r="K40" s="11" t="inlineStr">
-        <is>
-          <t>6890007</t>
-        </is>
-      </c>
+      <c r="K40" s="12" t="n"/>
       <c r="L40" s="12" t="n"/>
       <c r="M40" s="11" t="inlineStr">
         <is>
@@ -2199,18 +2207,42 @@
       <c r="A41" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="12" t="n"/>
-      <c r="E41" s="11" t="n"/>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Fita Dewi Yuniar</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Bacteriology</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>AgriBac Team</t>
+        </is>
+      </c>
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="12" t="n"/>
       <c r="H41" s="12" t="n"/>
       <c r="I41" s="12" t="n"/>
       <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>6890007</t>
+        </is>
+      </c>
       <c r="L41" s="12" t="n"/>
-      <c r="M41" s="12" t="n"/>
+      <c r="M41" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -2399,15 +2431,32 @@
       <c r="L52" s="12" t="n"/>
       <c r="M52" s="12" t="n"/>
     </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="12" t="n"/>
+      <c r="C53" s="12" t="n"/>
+      <c r="D53" s="12" t="n"/>
+      <c r="E53" s="11" t="n"/>
+      <c r="F53" s="12" t="n"/>
+      <c r="G53" s="12" t="n"/>
+      <c r="H53" s="12" t="n"/>
+      <c r="I53" s="12" t="n"/>
+      <c r="J53" s="12" t="n"/>
+      <c r="K53" s="12" t="n"/>
+      <c r="L53" s="12" t="n"/>
+      <c r="M53" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
